--- a/informationIII/12w/Book1.xlsx
+++ b/informationIII/12w/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kojor_fyn5sjo\2025\report\informationIII\12w\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B41114-7D7D-4DDE-AC36-9C24317CBC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E574559-E2F8-4D26-8EBA-6447BFDE36B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{ED173361-A60D-41CF-8FF4-1F6ED8866D47}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{ED173361-A60D-41CF-8FF4-1F6ED8866D47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="65">
   <si>
     <t>学籍番号</t>
   </si>
@@ -455,6 +455,10 @@
     <rPh sb="0" eb="2">
       <t>セイセキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長松 次郎</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -463,7 +467,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="184" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -519,17 +523,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -538,14 +539,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,6 +560,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44066150-5419-BE14-69DB-71E051059106}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1249680" y="2918460"/>
+          <a:ext cx="8229600" cy="2293620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -926,22 +990,22 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
+      <c r="A2" s="6">
         <v>26401</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="6">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="G2" t="s">
@@ -959,17 +1023,17 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>45818</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
@@ -985,17 +1049,17 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>45819</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" t="s">
         <v>18</v>
       </c>
@@ -1011,27 +1075,27 @@
       <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>45822</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
+      <c r="A5" s="6">
         <v>26205</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="6">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G5" t="s">
@@ -1049,17 +1113,17 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>45819</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
@@ -1075,17 +1139,17 @@
       <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
       <c r="G7" t="s">
         <v>33</v>
       </c>
@@ -1101,27 +1165,27 @@
       <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
-        <v>26401</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="6">
+        <v>26132</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="6">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G8" t="s">
@@ -1139,17 +1203,17 @@
       <c r="K8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>45818</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1165,17 +1229,17 @@
       <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45819</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="G10" t="s">
         <v>38</v>
       </c>
@@ -1191,12 +1255,22 @@
       <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>45820</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="A8:A10"/>
@@ -1205,19 +1279,11 @@
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E10"/>
     <mergeCell ref="F8:F10"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1301,7 +1367,7 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -1339,7 +1405,7 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -1377,7 +1443,7 @@
       <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>45822</v>
       </c>
     </row>
@@ -1415,7 +1481,7 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -1453,7 +1519,7 @@
       <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -1491,13 +1557,13 @@
       <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>44</v>
@@ -1529,13 +1595,13 @@
       <c r="K8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>45818</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
@@ -1567,13 +1633,13 @@
       <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45819</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>44</v>
@@ -1605,7 +1671,7 @@
       <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -1698,7 +1764,7 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -1736,7 +1802,7 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -1774,7 +1840,7 @@
       <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>45822</v>
       </c>
     </row>
@@ -1812,7 +1878,7 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -1850,7 +1916,7 @@
       <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -1888,13 +1954,13 @@
       <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>44</v>
@@ -1926,13 +1992,13 @@
       <c r="K8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>45818</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
@@ -1964,13 +2030,13 @@
       <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45819</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>44</v>
@@ -2002,183 +2068,183 @@
       <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="P13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>26401</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>18</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>26401</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="3">
         <v>65</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>45818</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>26205</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>19</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <v>26401</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="3">
         <v>42</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>45819</v>
       </c>
-      <c r="O15" s="5" t="s">
+      <c r="O15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="P15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>26401</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>18</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>26401</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="3">
         <v>79</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>45822</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="O16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="P16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="Q16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2188,160 +2254,160 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
         <v>26205</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="3">
         <v>76</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>45819</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="O17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="P17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="Q17" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>26205</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="3">
         <v>66</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>45820</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="O18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="P18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>26205</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="3">
         <v>90</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>45820</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="P19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q19" s="4" t="s">
+      <c r="Q19" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>26401</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="3">
         <v>87</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>45818</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="P20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="Q20" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="I21" s="5">
+      <c r="I21" s="4">
         <v>26401</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="3">
         <v>78</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>45819</v>
       </c>
-      <c r="O21" s="5" t="s">
+      <c r="O21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="Q21" s="4" t="s">
+      <c r="Q21" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="I22" s="5">
+      <c r="I22" s="4">
         <v>26401</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>45820</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="P22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="Q22" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2352,37 +2418,37 @@
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>
-      <c r="D41" s="3"/>
+      <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="D45" s="3"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1"/>
-      <c r="D46" s="3"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="1"/>
@@ -2494,7 +2560,7 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -2532,7 +2598,7 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -2570,7 +2636,7 @@
       <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>45822</v>
       </c>
     </row>
@@ -2608,7 +2674,7 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -2646,7 +2712,7 @@
       <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -2684,7 +2750,7 @@
       <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -2722,7 +2788,7 @@
       <c r="K8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -2760,7 +2826,7 @@
       <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -2798,7 +2864,7 @@
       <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -2811,130 +2877,130 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>26401</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>18</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>1</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>26401</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="3">
         <v>1</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="3">
         <v>65</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="3">
         <v>2</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>45818</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>26205</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>19</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>1</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>2</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <v>26401</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="4">
         <v>2</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="3">
         <v>42</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="3">
         <v>1</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>45819</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>26401</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>20</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>2</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>3</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>26401</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="3">
         <v>3</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="3">
         <v>79</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="3">
         <v>3</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>45822</v>
       </c>
     </row>
@@ -2944,19 +3010,19 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
         <v>26205</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="3">
         <v>2</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="3">
         <v>76</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="3">
         <v>3</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>45819</v>
       </c>
     </row>
@@ -2968,147 +3034,147 @@
       <c r="F18" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>26205</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="4">
         <v>4</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="3">
         <v>66</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="3">
         <v>2</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>45820</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>26205</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="3">
         <v>5</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="3">
         <v>90</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="3">
         <v>4</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>45820</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>1</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>1</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="5">
-        <v>26401</v>
-      </c>
-      <c r="J20" s="4">
+      <c r="I20" s="4">
+        <v>26132</v>
+      </c>
+      <c r="J20" s="3">
         <v>2</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="3">
         <v>87</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="3">
         <v>4</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>45818</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>2</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>2</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>2</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="5">
-        <v>26401</v>
-      </c>
-      <c r="J21" s="5">
+      <c r="I21" s="4">
+        <v>26132</v>
+      </c>
+      <c r="J21" s="4">
         <v>6</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="3">
         <v>78</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="3">
         <v>3</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>45819</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>3</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>3</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>3</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I22" s="5">
-        <v>26401</v>
-      </c>
-      <c r="J22" s="4">
+      <c r="I22" s="4">
+        <v>26132</v>
+      </c>
+      <c r="J22" s="3">
         <v>7</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="3">
         <v>4</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>45820</v>
       </c>
     </row>
@@ -3127,256 +3193,249 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="4" t="s">
+      <c r="E24" s="2"/>
+      <c r="F24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="4">
+      <c r="G25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I25" s="3">
         <v>1</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="3">
         <v>59</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="3">
         <v>1</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="O25" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>2</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="3">
         <v>2</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26" s="3">
         <v>69</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="3">
         <v>60</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="3">
         <v>2</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="O26" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>3</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="3">
         <v>3</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="3">
         <v>79</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="3">
         <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>4</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="3">
         <v>4</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K28" s="4">
+      <c r="K28" s="3">
         <v>100</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="3">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B29" s="4">
+      <c r="B29" s="3">
         <v>5</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B30" s="4">
+      <c r="B30" s="3">
         <v>6</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B31" s="4">
+      <c r="B31" s="3">
         <v>7</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>
-      <c r="D41" s="3"/>
+      <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="D45" s="3"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1"/>
-      <c r="D46" s="3"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="1"/>
@@ -3402,6 +3461,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3488,7 +3548,7 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -3526,7 +3586,7 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -3564,7 +3624,7 @@
       <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>45822</v>
       </c>
     </row>
@@ -3602,7 +3662,7 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -3640,7 +3700,7 @@
       <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -3678,7 +3738,7 @@
       <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -3716,7 +3776,7 @@
       <c r="K8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -3754,7 +3814,7 @@
       <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -3792,7 +3852,7 @@
       <c r="K10" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -4062,7 +4122,7 @@
       <c r="D38">
         <v>1</v>
       </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
@@ -4074,7 +4134,7 @@
       <c r="D39">
         <v>2</v>
       </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
@@ -4086,7 +4146,7 @@
       <c r="D40">
         <v>4</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
@@ -4098,7 +4158,7 @@
       <c r="D41">
         <v>2</v>
       </c>
-      <c r="E41" s="3"/>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
@@ -4110,7 +4170,7 @@
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="E42" s="3"/>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
@@ -4122,7 +4182,7 @@
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" s="3"/>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
@@ -4134,7 +4194,7 @@
       <c r="D44">
         <v>1</v>
       </c>
-      <c r="E44" s="3"/>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
@@ -4146,7 +4206,7 @@
       <c r="D45">
         <v>2</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
@@ -4158,7 +4218,7 @@
       <c r="D46">
         <v>3</v>
       </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="2"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
@@ -4216,7 +4276,7 @@
       <c r="A54" s="1">
         <v>1</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="2">
         <v>45818</v>
       </c>
     </row>
@@ -4224,7 +4284,7 @@
       <c r="A55" s="1">
         <v>2</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="2">
         <v>45819</v>
       </c>
     </row>
@@ -4232,7 +4292,7 @@
       <c r="A56" s="1">
         <v>3</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="2">
         <v>45820</v>
       </c>
     </row>
@@ -4240,7 +4300,7 @@
       <c r="A57" s="1">
         <v>4</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="2">
         <v>45822</v>
       </c>
     </row>
@@ -4267,7 +4327,7 @@
       <c r="B61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
@@ -4276,10 +4336,10 @@
       <c r="B62" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D63" s="3"/>
+      <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
@@ -4291,7 +4351,7 @@
       <c r="C64" t="s">
         <v>9</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
     </row>

--- a/informationIII/12w/Book1.xlsx
+++ b/informationIII/12w/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kojor_fyn5sjo\2025\report\informationIII\12w\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E574559-E2F8-4D26-8EBA-6447BFDE36B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D860A2-0AAA-4E6B-974F-EE6C0677E4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{ED173361-A60D-41CF-8FF4-1F6ED8866D47}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED173361-A60D-41CF-8FF4-1F6ED8866D47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="67">
   <si>
     <t>学籍番号</t>
   </si>
@@ -459,6 +459,19 @@
   </si>
   <si>
     <t>長松 次郎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械ロボティクス系</t>
+  </si>
+  <si>
+    <t>機械ロボティクス系</t>
+    <rPh sb="0" eb="2">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ケイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1183,7 +1196,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>43</v>
@@ -1261,6 +1274,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
@@ -1273,12 +1292,6 @@
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1575,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>43</v>
@@ -1613,7 +1626,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>43</v>
@@ -1651,7 +1664,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>43</v>
@@ -1678,6 +1691,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1972,7 +1986,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>43</v>
@@ -2010,7 +2024,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>43</v>
@@ -2048,7 +2062,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>43</v>
@@ -3756,7 +3770,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>43</v>
@@ -3794,7 +3808,7 @@
         <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>43</v>
@@ -3832,7 +3846,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>43</v>

--- a/informationIII/12w/Book1.xlsx
+++ b/informationIII/12w/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kojor_fyn5sjo\2025\report\informationIII\12w\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D860A2-0AAA-4E6B-974F-EE6C0677E4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCA5DC0-FB67-4416-BD8C-5425DD296420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED173361-A60D-41CF-8FF4-1F6ED8866D47}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{ED173361-A60D-41CF-8FF4-1F6ED8866D47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1274,12 +1274,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
@@ -1292,6 +1286,12 @@
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2220,19 +2220,19 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>43</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="I20" s="4">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>17</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="I21" s="4">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>37</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="I22" s="4">
-        <v>26401</v>
+        <v>26132</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>38</v>
